--- a/SQL_OMDB/rating.xlsx
+++ b/SQL_OMDB/rating.xlsx
@@ -464,37 +464,37 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Scream</t>
+          <t>Shrek</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20 Dec 1996</t>
+          <t>18 May 2001</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>111 min</t>
+          <t>90 min</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Horror, Mystery</t>
+          <t>Animation, Adventure, Comedy</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Wes Craven</t>
+          <t>Andrew Adamson, Vicky Jenson</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Unrated</t>
         </is>
       </c>
     </row>
@@ -504,32 +504,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Scream 2</t>
+          <t>Shrek 2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>12 Dec 1997</t>
+          <t>19 May 2004</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>120 min</t>
+          <t>93 min</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Horror, Mystery</t>
+          <t>Animation, Adventure, Comedy</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Wes Craven</t>
+          <t>Andrew Adamson, Kelly Asbury, Conrad Vernon</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -544,22 +544,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Scream 3</t>
+          <t>Scream</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>04 Feb 2000</t>
+          <t>20 Dec 1996</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>116 min</t>
+          <t>111 min</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">

--- a/SQL_OMDB/rating.xlsx
+++ b/SQL_OMDB/rating.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,25 +434,20 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>released</t>
+          <t>runtime</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>runtime</t>
+          <t>genre</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>genre</t>
+          <t>director</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
-        <is>
-          <t>director</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
         <is>
           <t>rating</t>
         </is>
@@ -464,115 +459,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Shrek</t>
+          <t>Ghostbusters</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>18 May 2001</t>
+          <t>105 min</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>90 min</t>
+          <t>Action, Comedy, Fantasy</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Animation, Adventure, Comedy</t>
+          <t>Ivan Reitman</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
-        <is>
-          <t>Andrew Adamson, Vicky Jenson</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Unrated</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Shrek 2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>19 May 2004</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>93 min</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Animation, Adventure, Comedy</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Andrew Adamson, Kelly Asbury, Conrad Vernon</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Unrated</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Scream</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>20 Dec 1996</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>111 min</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Horror, Mystery</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Wes Craven</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
         <is>
           <t>Unrated</t>
         </is>
